--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0840311E-6AA0-4435-BBCA-96FA5455825E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697CCAAF-EE59-4816-A737-A23EAE10322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="M3" sheetId="5" r:id="rId5"/>
     <sheet name="M4" sheetId="6" r:id="rId6"/>
     <sheet name="M5" sheetId="7" r:id="rId7"/>
+    <sheet name="M6" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="303">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -901,6 +902,90 @@
   </si>
   <si>
     <t>Added an extra section, which I later got to know, I should not be doing as this expands the scope, should have added this in the initial draft itself. Implemented basic info,pcc,null count. Added 2 sections (describe and value counts) they took lot of logical working</t>
+  </si>
+  <si>
+    <t>M6T1</t>
+  </si>
+  <si>
+    <t>M6T2</t>
+  </si>
+  <si>
+    <t>M6T3</t>
+  </si>
+  <si>
+    <t>Learn basics of DuckDB</t>
+  </si>
+  <si>
+    <t>Learn and understand how to implement DuckDB</t>
+  </si>
+  <si>
+    <t>Learning DuckDB as a technology is important to implement large dataset loading</t>
+  </si>
+  <si>
+    <t>Implement basic operation of viewing 10 records, selecting rows based on conditions</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>Simple operation to view recording using python duckdb sql helps to understand how to use duckdb for this project</t>
+  </si>
+  <si>
+    <t>Implement chunking using DuckDB and learn parquet</t>
+  </si>
+  <si>
+    <t>Trial of large dataset</t>
+  </si>
+  <si>
+    <t>Try out loading large datasets using duckdb and see if the scaling works</t>
+  </si>
+  <si>
+    <t>try out (5gb csv - duckdb - parquet - query)</t>
+  </si>
+  <si>
+    <t>M6T4</t>
+  </si>
+  <si>
+    <t>M6T5</t>
+  </si>
+  <si>
+    <t>M6T6</t>
+  </si>
+  <si>
+    <t>Introduce data manger and rewrite app.py</t>
+  </si>
+  <si>
+    <t>Introduce data manager concept to handle large and small datasets individually, rewrite sections of app.py to reflect this data difference</t>
+  </si>
+  <si>
+    <t>Migrate few of the current operations</t>
+  </si>
+  <si>
+    <t>missing values, white spaces,triming,duplicates and data type contents</t>
+  </si>
+  <si>
+    <t>Will mostly need work over the weekend as well to fit into schedule properly</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
+    <t>Will mostly need extra work compared to pandas as this requires SQL contents</t>
+  </si>
+  <si>
+    <t>Migrate information/analysis operations, and export</t>
+  </si>
+  <si>
+    <t>info,describe,correlation etc along with checking for export</t>
+  </si>
+  <si>
+    <t>(Tentative Dates) Scalability Features</t>
+  </si>
+  <si>
+    <t>22/9/2026</t>
+  </si>
+  <si>
+    <t>if size less than thres then pandas, else duckdb+parquet, largest change till date</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1047,6 +1132,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1720,7 +1808,7 @@
       <c r="F6" s="10">
         <v>46121</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="16">
         <v>46121</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -3734,4 +3822,318 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FCF995-1391-4EDC-83B6-2FCFE0A29871}">
+  <sheetPr>
+    <tabColor theme="5" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="35.7109375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="7">
+        <v>46304</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="7">
+        <v>46335</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697CCAAF-EE59-4816-A737-A23EAE10322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0A318C-40CA-4958-94A3-06A3FA6FCA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="303">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -1130,11 +1130,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1808,7 +1808,7 @@
       <c r="F6" s="10">
         <v>46121</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <v>46121</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -1942,20 +1942,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2331,20 +2331,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2644,20 +2644,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3033,20 +3033,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3499,20 +3499,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3848,20 +3848,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3918,10 +3918,10 @@
         <v>46304</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>95</v>
+        <v>19</v>
+      </c>
+      <c r="G3" s="7">
+        <v>46304</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>96</v>
@@ -3956,7 +3956,7 @@
         <v>46335</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>95</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0A318C-40CA-4958-94A3-06A3FA6FCA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1F4E39-BF2B-4D88-A4D9-63BD0C5035DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="303">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -937,9 +937,6 @@
     <t>Trial of large dataset</t>
   </si>
   <si>
-    <t>Try out loading large datasets using duckdb and see if the scaling works</t>
-  </si>
-  <si>
     <t>try out (5gb csv - duckdb - parquet - query)</t>
   </si>
   <si>
@@ -986,6 +983,9 @@
   </si>
   <si>
     <t>if size less than thres then pandas, else duckdb+parquet, largest change till date</t>
+  </si>
+  <si>
+    <t>Try out loading large datasets using duckdb and see if the scaling works (separate file, not app.py)</t>
   </si>
 </sst>
 </file>
@@ -3849,7 +3849,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -3956,10 +3956,10 @@
         <v>46335</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>95</v>
+        <v>19</v>
+      </c>
+      <c r="G4" s="7">
+        <v>46335</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>101</v>
@@ -3985,7 +3985,7 @@
         <v>285</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>48</v>
@@ -3994,7 +3994,7 @@
         <v>282</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>95</v>
@@ -4003,7 +4003,7 @@
         <v>101</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>95</v>
@@ -4017,19 +4017,19 @@
     </row>
     <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>292</v>
-      </c>
       <c r="D6" s="11" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>21</v>
@@ -4041,7 +4041,7 @@
         <v>101</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>95</v>
@@ -4055,19 +4055,19 @@
     </row>
     <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>294</v>
-      </c>
       <c r="D7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>21</v>
@@ -4079,7 +4079,7 @@
         <v>101</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>95</v>
@@ -4093,13 +4093,13 @@
     </row>
     <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>298</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>299</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>48</v>
@@ -4117,7 +4117,7 @@
         <v>101</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>95</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1F4E39-BF2B-4D88-A4D9-63BD0C5035DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3ABFE9-338C-42B3-9600-9B07E3D344B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -937,9 +937,6 @@
     <t>Trial of large dataset</t>
   </si>
   <si>
-    <t>try out (5gb csv - duckdb - parquet - query)</t>
-  </si>
-  <si>
     <t>M6T4</t>
   </si>
   <si>
@@ -982,10 +979,13 @@
     <t>22/9/2026</t>
   </si>
   <si>
-    <t>if size less than thres then pandas, else duckdb+parquet, largest change till date</t>
-  </si>
-  <si>
     <t>Try out loading large datasets using duckdb and see if the scaling works (separate file, not app.py)</t>
+  </si>
+  <si>
+    <t>try out (9gb csv - duckdb - query)</t>
+  </si>
+  <si>
+    <t>if size less than thres then pandas, else duckdb+parquet, largest change till date. Research on how to implement data manager layers</t>
   </si>
 </sst>
 </file>
@@ -3849,7 +3849,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -3985,7 +3985,7 @@
         <v>285</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>48</v>
@@ -3994,45 +3994,45 @@
         <v>282</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>95</v>
+        <v>282</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>101</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>287</v>
-      </c>
       <c r="B6" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>291</v>
-      </c>
       <c r="D6" s="11" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>95</v>
@@ -4041,7 +4041,7 @@
         <v>101</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>95</v>
@@ -4055,19 +4055,19 @@
     </row>
     <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>293</v>
-      </c>
       <c r="D7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>21</v>
@@ -4079,7 +4079,7 @@
         <v>101</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>95</v>
@@ -4093,13 +4093,13 @@
     </row>
     <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>298</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>48</v>
@@ -4117,7 +4117,7 @@
         <v>101</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>95</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing\docs\09-Project_Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3ABFE9-338C-42B3-9600-9B07E3D344B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF4198F-0B27-47F9-828E-34FEB7E6ACF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="307">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -970,9 +970,6 @@
     <t>Migrate information/analysis operations, and export</t>
   </si>
   <si>
-    <t>info,describe,correlation etc along with checking for export</t>
-  </si>
-  <si>
     <t>(Tentative Dates) Scalability Features</t>
   </si>
   <si>
@@ -986,6 +983,21 @@
   </si>
   <si>
     <t>if size less than thres then pandas, else duckdb+parquet, largest change till date. Research on how to implement data manager layers</t>
+  </si>
+  <si>
+    <t>Complications with respect to DuckDB and Streamlit data handling</t>
+  </si>
+  <si>
+    <t>Scope adjustment,reevaluate the target functionality</t>
+  </si>
+  <si>
+    <t>Above</t>
+  </si>
+  <si>
+    <t>29/09/2026</t>
+  </si>
+  <si>
+    <t>info,describe etc along with checking for export</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1057,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1055,6 +1067,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1086,7 +1104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1135,6 +1153,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3840,16 +3861,16 @@
     <col min="6" max="6" width="10.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="35.7109375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" style="6" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" style="6" customWidth="1"/>
     <col min="13" max="13" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -3891,13 +3912,13 @@
       <c r="I2" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3929,13 +3950,13 @@
       <c r="I3" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="J3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3967,13 +3988,13 @@
       <c r="I4" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="J4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3985,7 +4006,7 @@
         <v>285</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>48</v>
@@ -4003,15 +4024,15 @@
         <v>101</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4029,31 +4050,31 @@
         <v>48</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>95</v>
+        <v>298</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>101</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>287</v>
       </c>
@@ -4066,11 +4087,11 @@
       <c r="D7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="17" t="s">
         <v>294</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>95</v>
@@ -4081,17 +4102,17 @@
       <c r="I7" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="J7" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>288</v>
       </c>
@@ -4099,12 +4120,12 @@
         <v>296</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="17" t="s">
         <v>247</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -4119,14 +4140,14 @@
       <c r="I8" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>95</v>
+      <c r="J8" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF4198F-0B27-47F9-828E-34FEB7E6ACF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E17B12-8579-4188-8EF5-2C7AC60A3CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="308">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -955,9 +955,6 @@
     <t>Migrate few of the current operations</t>
   </si>
   <si>
-    <t>missing values, white spaces,triming,duplicates and data type contents</t>
-  </si>
-  <si>
     <t>Will mostly need work over the weekend as well to fit into schedule properly</t>
   </si>
   <si>
@@ -973,9 +970,6 @@
     <t>(Tentative Dates) Scalability Features</t>
   </si>
   <si>
-    <t>22/9/2026</t>
-  </si>
-  <si>
     <t>Try out loading large datasets using duckdb and see if the scaling works (separate file, not app.py)</t>
   </si>
   <si>
@@ -998,6 +992,15 @@
   </si>
   <si>
     <t>info,describe etc along with checking for export</t>
+  </si>
+  <si>
+    <t>missing values,white spaces,triming,duplicates and data type contents</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>M6T4,M6T6</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1151,10 +1154,13 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1963,20 +1969,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2352,20 +2358,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2665,20 +2671,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3054,20 +3060,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3520,20 +3526,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3869,20 +3875,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4006,7 +4012,7 @@
         <v>285</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>48</v>
@@ -4024,7 +4030,7 @@
         <v>101</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>95</v>
@@ -4050,19 +4056,19 @@
         <v>48</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>101</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>95</v>
@@ -4082,34 +4088,34 @@
         <v>291</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>161</v>
+      <c r="E7" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>101</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>247</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -4117,15 +4123,15 @@
         <v>288</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="16" t="s">
         <v>247</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -4135,19 +4141,19 @@
         <v>95</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>101</v>
+        <v>307</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E17B12-8579-4188-8EF5-2C7AC60A3CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00094EBE-0926-443D-83C3-761BCA523970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -994,13 +994,13 @@
     <t>info,describe etc along with checking for export</t>
   </si>
   <si>
-    <t>missing values,white spaces,triming,duplicates and data type contents</t>
-  </si>
-  <si>
     <t>22/09/2026</t>
   </si>
   <si>
     <t>M6T4,M6T6</t>
+  </si>
+  <si>
+    <t>remove redundant columns,remove duplicates,trim whitespaces,handle casing,missing values</t>
   </si>
 </sst>
 </file>
@@ -1160,8 +1160,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4056,13 +4056,13 @@
         <v>48</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>101</v>
@@ -4096,10 +4096,10 @@
       <c r="E7" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>247</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -4126,7 +4126,7 @@
         <v>295</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>48</v>
@@ -4137,11 +4137,11 @@
       <c r="F8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>95</v>
+      <c r="G8" s="18" t="s">
+        <v>303</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>294</v>
@@ -4162,5 +4162,6 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00094EBE-0926-443D-83C3-761BCA523970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BF631E-499D-452C-A156-AA2E6D552A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1157,10 +1157,10 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1969,20 +1969,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2358,20 +2358,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2671,20 +2671,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3060,20 +3060,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3526,20 +3526,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3875,20 +3875,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4135,9 +4135,9 @@
         <v>247</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>303</v>
       </c>
       <c r="H8" s="5" t="s">

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BF631E-499D-452C-A156-AA2E6D552A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDED69FB-008F-458F-BCC2-4BB57C8EAC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="317" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="2595" windowWidth="20730" windowHeight="11760" tabRatio="669" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="M4" sheetId="6" r:id="rId6"/>
     <sheet name="M5" sheetId="7" r:id="rId7"/>
     <sheet name="M6" sheetId="8" r:id="rId8"/>
+    <sheet name="M7" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="332">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -787,12 +788,6 @@
   </si>
   <si>
     <t>25/09/2026</t>
-  </si>
-  <si>
-    <t>28/09/2026</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
   </si>
   <si>
     <t>Remaining time (half october + 15 days of november) can be allocated to working on advance scope (future scope). The project's main scope will have already finished.</t>
@@ -1002,12 +997,90 @@
   <si>
     <t>remove redundant columns,remove duplicates,trim whitespaces,handle casing,missing values</t>
   </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>M7T1</t>
+  </si>
+  <si>
+    <t>M7T2</t>
+  </si>
+  <si>
+    <t>M7T3</t>
+  </si>
+  <si>
+    <t>M7T4</t>
+  </si>
+  <si>
+    <t>M7T5</t>
+  </si>
+  <si>
+    <t>Finish M6</t>
+  </si>
+  <si>
+    <t>Decide based test scenarios and what modules to test</t>
+  </si>
+  <si>
+    <t>Test module and scenario decision</t>
+  </si>
+  <si>
+    <t>Decide primary contents for what to test and what sections to test</t>
+  </si>
+  <si>
+    <t>Manual and automated testing (pytest?)</t>
+  </si>
+  <si>
+    <t>Learn basic pytest and also try out manual testing</t>
+  </si>
+  <si>
+    <t>Unit Testing</t>
+  </si>
+  <si>
+    <t>Each module seperately tested</t>
+  </si>
+  <si>
+    <t>Integration Testing</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>Combine modules under 1 functionality and test</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>Trial testing scripts for pytest and checkout manual practices for testing</t>
+  </si>
+  <si>
+    <t>File by file testing for each module and script</t>
+  </si>
+  <si>
+    <t>Check integration  between 2 modules main for analysis section</t>
+  </si>
+  <si>
+    <t>Full dataset run and Report</t>
+  </si>
+  <si>
+    <t>Run full dataset pipeline, and compile a small report of test passing and failing</t>
+  </si>
+  <si>
+    <t>Full run of dataset along with a sheet or report for testing section</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1055,6 +1128,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1107,7 +1187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1162,6 +1242,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1813,7 +1920,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>216</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1839,10 +1946,10 @@
         <v>46121</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -1850,7 +1957,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>52</v>
@@ -1861,17 +1968,17 @@
       <c r="E7" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>214</v>
+      <c r="F7" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="G7" s="20">
+        <v>46032</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J7" s="12" t="s">
         <v>246</v>
@@ -1887,11 +1994,11 @@
       <c r="C8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>248</v>
+      <c r="D8" s="7">
+        <v>46152</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>214</v>
@@ -1900,13 +2007,13 @@
         <v>214</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -1938,7 +2045,7 @@
         <v>21</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -2750,7 +2857,7 @@
         <v>158</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>95</v>
@@ -2788,7 +2895,7 @@
         <v>159</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>95</v>
@@ -2826,7 +2933,7 @@
         <v>158</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>95</v>
@@ -2864,7 +2971,7 @@
         <v>158</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>95</v>
@@ -2902,7 +3009,7 @@
         <v>160</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>95</v>
@@ -2940,7 +3047,7 @@
         <v>160</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>95</v>
@@ -2978,7 +3085,7 @@
         <v>127</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>95</v>
@@ -3016,7 +3123,7 @@
         <v>158</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>95</v>
@@ -3139,7 +3246,7 @@
         <v>127</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>95</v>
@@ -3177,7 +3284,7 @@
         <v>70</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>95</v>
@@ -3215,7 +3322,7 @@
         <v>127</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>95</v>
@@ -3367,7 +3474,7 @@
         <v>70</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>95</v>
@@ -3405,7 +3512,7 @@
         <v>192</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>95</v>
@@ -3605,7 +3712,7 @@
         <v>96</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>95</v>
@@ -3643,7 +3750,7 @@
         <v>212</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>95</v>
@@ -3681,7 +3788,7 @@
         <v>212</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>95</v>
@@ -3719,7 +3826,7 @@
         <v>212</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>95</v>
@@ -3751,13 +3858,13 @@
         <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>213</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -3783,13 +3890,13 @@
         <v>19</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>221</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>95</v>
@@ -3830,7 +3937,7 @@
         <v>101</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>95</v>
@@ -3876,7 +3983,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -3930,13 +4037,13 @@
     </row>
     <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>48</v>
@@ -3954,7 +4061,7 @@
         <v>96</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>95</v>
@@ -3968,13 +4075,13 @@
     </row>
     <row r="4" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>48</v>
@@ -3992,7 +4099,7 @@
         <v>101</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>95</v>
@@ -4006,31 +4113,31 @@
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>101</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>95</v>
@@ -4044,31 +4151,31 @@
     </row>
     <row r="6" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>101</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>95</v>
@@ -4082,19 +4189,19 @@
     </row>
     <row r="7" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>291</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>293</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>19</v>
@@ -4106,27 +4213,27 @@
         <v>101</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>247</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>48</v>
@@ -4138,22 +4245,22 @@
         <v>19</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -4164,4 +4271,287 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98117FD9-99EB-42F8-9A4F-DBDF7BE0E77E}">
+  <sheetPr>
+    <tabColor theme="5" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="22"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="22"/>
+    </row>
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="27">
+        <v>46213</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="M3" s="22"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="27">
+        <v>46275</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="L4" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4" s="22"/>
+    </row>
+    <row r="5" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" s="22"/>
+    </row>
+    <row r="6" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="M6" s="22"/>
+    </row>
+    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="M7" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A297D34-8868-4335-8395-7294516EBBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9CCD18-073C-4885-A021-14688B1296AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="669" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="332">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -1074,9 +1074,6 @@
   </si>
   <si>
     <t>Full run of dataset along with a sheet or report for testing section</t>
-  </si>
-  <si>
-    <t>In Progres</t>
   </si>
 </sst>
 </file>
@@ -4390,10 +4387,10 @@
         <v>46275</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>95</v>
+        <v>19</v>
+      </c>
+      <c r="G4" s="7">
+        <v>46275</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>309</v>
@@ -4429,7 +4426,7 @@
         <v>323</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>95</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9CCD18-073C-4885-A021-14688B1296AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42834173-66C9-4E7D-8B66-AA8A0433C5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="669" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="328" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documents" sheetId="3" r:id="rId1"/>
@@ -1064,9 +1064,6 @@
     <t>File by file testing for each module and script</t>
   </si>
   <si>
-    <t>Check integration  between 2 modules main for analysis section</t>
-  </si>
-  <si>
     <t>Full dataset run and Report</t>
   </si>
   <si>
@@ -1074,6 +1071,9 @@
   </si>
   <si>
     <t>Full run of dataset along with a sheet or report for testing section</t>
+  </si>
+  <si>
+    <t>Check integration  between 2 modules main for analysis section,perform manually</t>
   </si>
 </sst>
 </file>
@@ -4426,10 +4426,10 @@
         <v>323</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>101</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="M5" s="6"/>
     </row>
-    <row r="6" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>312</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>325</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -4474,7 +4474,7 @@
         <v>101</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>95</v>
@@ -4492,10 +4492,10 @@
         <v>313</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>329</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>330</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>48</v>
@@ -4513,7 +4513,7 @@
         <v>101</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>95</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42834173-66C9-4E7D-8B66-AA8A0433C5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2463D93C-9A3D-48E1-AB52-7DAF5B8EE408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="328" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="333">
   <si>
     <t>Milestone Name</t>
   </si>
@@ -1074,6 +1074,9 @@
   </si>
   <si>
     <t>Check integration  between 2 modules main for analysis section,perform manually</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
   </si>
 </sst>
 </file>
@@ -4465,10 +4468,10 @@
         <v>325</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>95</v>
+        <v>332</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>101</v>
@@ -4504,7 +4507,7 @@
         <v>306</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>95</v>

--- a/docs/09-Project_Plan/9-Project_Plan.xlsx
+++ b/docs/09-Project_Plan/9-Project_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College_Backup\BTech_Internship\Persistent_Project\Dataset-Pipeline\NoCodeDatasetPreprocessing_DuckDB_Attempt\docs\09-Project_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2463D93C-9A3D-48E1-AB52-7DAF5B8EE408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E630D2B-6ACE-470D-B332-3EC276789C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="328" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4507,10 +4507,10 @@
         <v>306</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>101</v>
